--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546979</v>
+        <v>122546975</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>78392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6446</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776599</v>
+        <v>776537</v>
       </c>
       <c r="R2" t="n">
-        <v>7104894</v>
+        <v>7104960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B3" t="n">
-        <v>78388</v>
+        <v>92100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,20 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R3" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +890,7 @@
         <v>122546983</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -894,6 +904,11 @@
       </c>
       <c r="E4" t="n">
         <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546979</v>
+        <v>122546983</v>
       </c>
       <c r="B3" t="n">
-        <v>92100</v>
+        <v>92148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776599</v>
+        <v>776589</v>
       </c>
       <c r="R3" t="n">
-        <v>7104894</v>
+        <v>7104910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546983</v>
+        <v>122546979</v>
       </c>
       <c r="B4" t="n">
-        <v>92135</v>
+        <v>92113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776589</v>
+        <v>776599</v>
       </c>
       <c r="R4" t="n">
-        <v>7104910</v>
+        <v>7104894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B2" t="n">
-        <v>78392</v>
+        <v>92114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R2" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122546983</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546979</v>
+        <v>122546975</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>78392</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776599</v>
+        <v>776537</v>
       </c>
       <c r="R4" t="n">
-        <v>7104894</v>
+        <v>7104960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546979</v>
+        <v>122546983</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776599</v>
+        <v>776589</v>
       </c>
       <c r="R2" t="n">
-        <v>7104894</v>
+        <v>7104910</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546983</v>
+        <v>122546975</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>78392</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776589</v>
+        <v>776537</v>
       </c>
       <c r="R3" t="n">
-        <v>7104910</v>
+        <v>7104960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B4" t="n">
-        <v>78392</v>
+        <v>92114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R4" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546983</v>
       </c>
       <c r="B2" t="n">
-        <v>92149</v>
+        <v>92150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B3" t="n">
-        <v>78392</v>
+        <v>92115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R3" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546979</v>
+        <v>122546975</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>78393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776599</v>
+        <v>776537</v>
       </c>
       <c r="R4" t="n">
-        <v>7104894</v>
+        <v>7104960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546983</v>
+        <v>122546979</v>
       </c>
       <c r="B2" t="n">
-        <v>92150</v>
+        <v>92118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776589</v>
+        <v>776599</v>
       </c>
       <c r="R2" t="n">
-        <v>7104910</v>
+        <v>7104894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546979</v>
+        <v>122546983</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776599</v>
+        <v>776589</v>
       </c>
       <c r="R3" t="n">
-        <v>7104894</v>
+        <v>7104910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122546975</v>
       </c>
       <c r="B4" t="n">
-        <v>78393</v>
+        <v>78396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546979</v>
+        <v>122546975</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>78396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776599</v>
+        <v>776537</v>
       </c>
       <c r="R2" t="n">
-        <v>7104894</v>
+        <v>7104960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546983</v>
+        <v>122546979</v>
       </c>
       <c r="B3" t="n">
-        <v>92153</v>
+        <v>92118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776589</v>
+        <v>776599</v>
       </c>
       <c r="R3" t="n">
-        <v>7104910</v>
+        <v>7104894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546975</v>
+        <v>122546983</v>
       </c>
       <c r="B4" t="n">
-        <v>78396</v>
+        <v>92153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776537</v>
+        <v>776589</v>
       </c>
       <c r="R4" t="n">
-        <v>7104960</v>
+        <v>7104910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B2" t="n">
-        <v>78396</v>
+        <v>92221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R2" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546979</v>
+        <v>122546975</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>78498</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776599</v>
+        <v>776537</v>
       </c>
       <c r="R3" t="n">
-        <v>7104894</v>
+        <v>7104960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122546983</v>
       </c>
       <c r="B4" t="n">
-        <v>92153</v>
+        <v>92256</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546979</v>
       </c>
       <c r="B2" t="n">
-        <v>92221</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122546975</v>
       </c>
       <c r="B3" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122546983</v>
       </c>
       <c r="B4" t="n">
-        <v>92256</v>
+        <v>92260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546979</v>
+        <v>122546983</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>92260</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776599</v>
+        <v>776589</v>
       </c>
       <c r="R2" t="n">
-        <v>7104894</v>
+        <v>7104910</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R3" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546983</v>
+        <v>122546975</v>
       </c>
       <c r="B4" t="n">
-        <v>92260</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776589</v>
+        <v>776537</v>
       </c>
       <c r="R4" t="n">
-        <v>7104910</v>
+        <v>7104960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546979</v>
+        <v>122546975</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776599</v>
+        <v>776537</v>
       </c>
       <c r="R3" t="n">
-        <v>7104894</v>
+        <v>7104960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R4" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546983</v>
+        <v>122546975</v>
       </c>
       <c r="B2" t="n">
-        <v>92260</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776589</v>
+        <v>776537</v>
       </c>
       <c r="R2" t="n">
-        <v>7104910</v>
+        <v>7104960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546975</v>
+        <v>122546983</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>92260</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776537</v>
+        <v>776589</v>
       </c>
       <c r="R3" t="n">
-        <v>7104960</v>
+        <v>7104910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546975</v>
+        <v>122546979</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776537</v>
+        <v>776599</v>
       </c>
       <c r="R2" t="n">
-        <v>7104960</v>
+        <v>7104894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +779,7 @@
         <v>122546983</v>
       </c>
       <c r="B3" t="n">
-        <v>92260</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546979</v>
+        <v>122546975</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776599</v>
+        <v>776537</v>
       </c>
       <c r="R4" t="n">
-        <v>7104894</v>
+        <v>7104960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 37889-2023 artfynd.xlsx
+++ b/artfynd/A 37889-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546979</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546983</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546975</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>